--- a/Fortran/results/Test_results.xlsx
+++ b/Fortran/results/Test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\proek\Documents\GitHub\ModAB-Root-Finding\Fortran\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DB781E-9DC0-49C1-A017-5BB2927719AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBB1433-71F2-4E6B-A7A1-B360BF188051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{901E7075-F730-4135-A5B3-71A5C4E5AAAF}"/>
   </bookViews>
@@ -2396,7 +2396,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO237"/>
+  <dimension ref="A1:BO236"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.26953125" customWidth="1"/>
@@ -57089,7 +57089,9 @@
       </c>
     </row>
     <row r="227" spans="1:67" x14ac:dyDescent="0.35">
-      <c r="A227" s="11"/>
+      <c r="A227" s="11" t="s">
+        <v>214</v>
+      </c>
       <c r="B227" s="11"/>
       <c r="C227" s="11"/>
       <c r="D227" s="11"/>
@@ -58455,77 +58457,6 @@
       <c r="BN236" s="11"/>
       <c r="BO236" s="11"/>
     </row>
-    <row r="237" spans="1:67" x14ac:dyDescent="0.35">
-      <c r="A237" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="B237" s="11"/>
-      <c r="C237" s="11"/>
-      <c r="D237" s="11"/>
-      <c r="E237" s="11"/>
-      <c r="F237" s="11"/>
-      <c r="G237" s="11"/>
-      <c r="H237" s="11"/>
-      <c r="I237" s="11"/>
-      <c r="J237" s="11"/>
-      <c r="K237" s="11"/>
-      <c r="L237" s="11"/>
-      <c r="M237" s="11"/>
-      <c r="N237" s="11"/>
-      <c r="O237" s="11"/>
-      <c r="P237" s="11"/>
-      <c r="Q237" s="11"/>
-      <c r="R237" s="11"/>
-      <c r="S237" s="11"/>
-      <c r="T237" s="11"/>
-      <c r="U237" s="11"/>
-      <c r="V237" s="11"/>
-      <c r="W237" s="11"/>
-      <c r="X237" s="11"/>
-      <c r="Y237" s="11"/>
-      <c r="Z237" s="11"/>
-      <c r="AA237" s="11"/>
-      <c r="AB237" s="11"/>
-      <c r="AC237" s="11"/>
-      <c r="AD237" s="11"/>
-      <c r="AE237" s="11"/>
-      <c r="AF237" s="11"/>
-      <c r="AG237" s="11"/>
-      <c r="AH237" s="11"/>
-      <c r="AI237" s="11"/>
-      <c r="AJ237" s="11"/>
-      <c r="AK237" s="11"/>
-      <c r="AL237" s="11"/>
-      <c r="AM237" s="11"/>
-      <c r="AN237" s="11"/>
-      <c r="AO237" s="11"/>
-      <c r="AP237" s="11"/>
-      <c r="AQ237" s="11"/>
-      <c r="AR237" s="11"/>
-      <c r="AS237" s="11"/>
-      <c r="AT237" s="11"/>
-      <c r="AU237" s="11"/>
-      <c r="AV237" s="11"/>
-      <c r="AW237" s="11"/>
-      <c r="AX237" s="11"/>
-      <c r="AY237" s="11"/>
-      <c r="AZ237" s="11"/>
-      <c r="BA237" s="11"/>
-      <c r="BB237" s="11"/>
-      <c r="BC237" s="11"/>
-      <c r="BD237" s="11"/>
-      <c r="BE237" s="11"/>
-      <c r="BF237" s="11"/>
-      <c r="BG237" s="11"/>
-      <c r="BH237" s="11"/>
-      <c r="BI237" s="11"/>
-      <c r="BJ237" s="11"/>
-      <c r="BK237" s="11"/>
-      <c r="BL237" s="11"/>
-      <c r="BM237" s="11"/>
-      <c r="BN237" s="11"/>
-      <c r="BO237" s="11"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="F3:Y225">
     <cfRule type="colorScale" priority="4">
@@ -58559,8 +58490,8 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.55118110236220474" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="22" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="41" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Fortran/results/Test_results.xlsx
+++ b/Fortran/results/Test_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\proek\Documents\GitHub\ModAB-Root-Finding\Fortran\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98C94332-1C3E-4467-A034-DBF09078F86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F88AAD-A1BD-451F-819F-ACC799478223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{901E7075-F730-4135-A5B3-71A5C4E5AAAF}"/>
   </bookViews>
@@ -8815,7 +8815,7 @@
     <numFmt numFmtId="165" formatCode="0.000E+00"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="47" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9166,14 +9166,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -9336,7 +9328,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9476,9 +9468,6 @@
     <xf numFmtId="2" fontId="38" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9542,7 +9531,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8D166447-D689-4ADE-8B9D-041E58ED6DF7}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -9569,6 +9558,26 @@
         <i val="0"/>
         <u/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -11551,7 +11560,7 @@
       <c r="E3" s="20">
         <v>1.8954942670339801</v>
       </c>
-      <c r="F3" s="49">
+      <c r="F3" s="16">
         <v>45</v>
       </c>
       <c r="G3" s="16">
@@ -11784,10 +11793,10 @@
       <c r="A4" s="14">
         <v>2</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="C4" s="54"/>
+      <c r="C4" s="53"/>
       <c r="D4" s="27" t="s">
         <v>66</v>
       </c>
@@ -12027,8 +12036,8 @@
       <c r="A5" s="14">
         <v>3</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="55"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="27" t="s">
         <v>67</v>
       </c>
@@ -12268,8 +12277,8 @@
       <c r="A6" s="14">
         <v>4</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="55"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="54"/>
       <c r="D6" s="27" t="s">
         <v>68</v>
       </c>
@@ -12509,8 +12518,8 @@
       <c r="A7" s="14">
         <v>5</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="55"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="54"/>
       <c r="D7" s="27" t="s">
         <v>69</v>
       </c>
@@ -12750,8 +12759,8 @@
       <c r="A8" s="14">
         <v>6</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="55"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="54"/>
       <c r="D8" s="27" t="s">
         <v>75</v>
       </c>
@@ -12991,8 +13000,8 @@
       <c r="A9" s="14">
         <v>7</v>
       </c>
-      <c r="B9" s="52"/>
-      <c r="C9" s="55"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="54"/>
       <c r="D9" s="27" t="s">
         <v>74</v>
       </c>
@@ -13232,8 +13241,8 @@
       <c r="A10" s="14">
         <v>8</v>
       </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="55"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="54"/>
       <c r="D10" s="27" t="s">
         <v>73</v>
       </c>
@@ -13473,8 +13482,8 @@
       <c r="A11" s="14">
         <v>9</v>
       </c>
-      <c r="B11" s="52"/>
-      <c r="C11" s="55"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="54"/>
       <c r="D11" s="27" t="s">
         <v>72</v>
       </c>
@@ -13714,8 +13723,8 @@
       <c r="A12" s="14">
         <v>10</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="55"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="54"/>
       <c r="D12" s="27" t="s">
         <v>71</v>
       </c>
@@ -13955,8 +13964,8 @@
       <c r="A13" s="14">
         <v>11</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="56"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="55"/>
       <c r="D13" s="27" t="s">
         <v>70</v>
       </c>
@@ -14196,7 +14205,7 @@
       <c r="A14" s="14">
         <v>12</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="50" t="s">
         <v>214</v>
       </c>
       <c r="C14" s="26">
@@ -14441,7 +14450,7 @@
       <c r="A15" s="14">
         <v>12</v>
       </c>
-      <c r="B15" s="52"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="26">
         <v>100</v>
       </c>
@@ -14684,7 +14693,7 @@
       <c r="A16" s="14">
         <v>12</v>
       </c>
-      <c r="B16" s="53"/>
+      <c r="B16" s="52"/>
       <c r="C16" s="26">
         <v>200</v>
       </c>
@@ -15413,7 +15422,7 @@
       <c r="A19" s="14">
         <v>15</v>
       </c>
-      <c r="B19" s="57" t="s">
+      <c r="B19" s="56" t="s">
         <v>63</v>
       </c>
       <c r="C19" s="26">
@@ -15658,7 +15667,7 @@
       <c r="A20" s="14">
         <v>15</v>
       </c>
-      <c r="B20" s="58"/>
+      <c r="B20" s="57"/>
       <c r="C20" s="26">
         <v>6</v>
       </c>
@@ -15901,7 +15910,7 @@
       <c r="A21" s="14">
         <v>15</v>
       </c>
-      <c r="B21" s="58"/>
+      <c r="B21" s="57"/>
       <c r="C21" s="26">
         <v>8</v>
       </c>
@@ -16144,7 +16153,7 @@
       <c r="A22" s="14">
         <v>15</v>
       </c>
-      <c r="B22" s="58"/>
+      <c r="B22" s="57"/>
       <c r="C22" s="26">
         <v>10</v>
       </c>
@@ -16387,7 +16396,7 @@
       <c r="A23" s="14">
         <v>15</v>
       </c>
-      <c r="B23" s="59"/>
+      <c r="B23" s="58"/>
       <c r="C23" s="26">
         <v>12</v>
       </c>
@@ -16630,7 +16639,7 @@
       <c r="A24" s="14">
         <v>16</v>
       </c>
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="56" t="s">
         <v>62</v>
       </c>
       <c r="C24" s="26">
@@ -16875,7 +16884,7 @@
       <c r="A25" s="14">
         <v>16</v>
       </c>
-      <c r="B25" s="58"/>
+      <c r="B25" s="57"/>
       <c r="C25" s="26">
         <v>6</v>
       </c>
@@ -17118,7 +17127,7 @@
       <c r="A26" s="14">
         <v>16</v>
       </c>
-      <c r="B26" s="58"/>
+      <c r="B26" s="57"/>
       <c r="C26" s="26">
         <v>8</v>
       </c>
@@ -17361,7 +17370,7 @@
       <c r="A27" s="14">
         <v>16</v>
       </c>
-      <c r="B27" s="58"/>
+      <c r="B27" s="57"/>
       <c r="C27" s="26">
         <v>10</v>
       </c>
@@ -17604,7 +17613,7 @@
       <c r="A28" s="14">
         <v>16</v>
       </c>
-      <c r="B28" s="59"/>
+      <c r="B28" s="58"/>
       <c r="C28" s="26">
         <v>12</v>
       </c>
@@ -17847,7 +17856,7 @@
       <c r="A29" s="14">
         <v>17</v>
       </c>
-      <c r="B29" s="57" t="s">
+      <c r="B29" s="56" t="s">
         <v>62</v>
       </c>
       <c r="C29" s="26">
@@ -18092,7 +18101,7 @@
       <c r="A30" s="14">
         <v>17</v>
       </c>
-      <c r="B30" s="58"/>
+      <c r="B30" s="57"/>
       <c r="C30" s="26">
         <v>10</v>
       </c>
@@ -18335,7 +18344,7 @@
       <c r="A31" s="14">
         <v>17</v>
       </c>
-      <c r="B31" s="58"/>
+      <c r="B31" s="57"/>
       <c r="C31" s="26">
         <v>12</v>
       </c>
@@ -18578,7 +18587,7 @@
       <c r="A32" s="14">
         <v>17</v>
       </c>
-      <c r="B32" s="59"/>
+      <c r="B32" s="58"/>
       <c r="C32" s="26">
         <v>14</v>
       </c>
@@ -19064,7 +19073,7 @@
       <c r="A34" s="14">
         <v>19</v>
       </c>
-      <c r="B34" s="57" t="s">
+      <c r="B34" s="56" t="s">
         <v>269</v>
       </c>
       <c r="C34" s="26">
@@ -19309,7 +19318,7 @@
       <c r="A35" s="14">
         <v>19</v>
       </c>
-      <c r="B35" s="58"/>
+      <c r="B35" s="57"/>
       <c r="C35" s="26">
         <v>2</v>
       </c>
@@ -19552,7 +19561,7 @@
       <c r="A36" s="14">
         <v>19</v>
       </c>
-      <c r="B36" s="58"/>
+      <c r="B36" s="57"/>
       <c r="C36" s="26">
         <v>3</v>
       </c>
@@ -19795,7 +19804,7 @@
       <c r="A37" s="14">
         <v>19</v>
       </c>
-      <c r="B37" s="58"/>
+      <c r="B37" s="57"/>
       <c r="C37" s="26">
         <v>4</v>
       </c>
@@ -20038,7 +20047,7 @@
       <c r="A38" s="14">
         <v>19</v>
       </c>
-      <c r="B38" s="58"/>
+      <c r="B38" s="57"/>
       <c r="C38" s="26">
         <v>5</v>
       </c>
@@ -20281,7 +20290,7 @@
       <c r="A39" s="14">
         <v>19</v>
       </c>
-      <c r="B39" s="58"/>
+      <c r="B39" s="57"/>
       <c r="C39" s="26">
         <v>10</v>
       </c>
@@ -20524,7 +20533,7 @@
       <c r="A40" s="14">
         <v>19</v>
       </c>
-      <c r="B40" s="58"/>
+      <c r="B40" s="57"/>
       <c r="C40" s="26">
         <v>20</v>
       </c>
@@ -20767,7 +20776,7 @@
       <c r="A41" s="14">
         <v>19</v>
       </c>
-      <c r="B41" s="58"/>
+      <c r="B41" s="57"/>
       <c r="C41" s="26">
         <v>40</v>
       </c>
@@ -21010,7 +21019,7 @@
       <c r="A42" s="14">
         <v>19</v>
       </c>
-      <c r="B42" s="58"/>
+      <c r="B42" s="57"/>
       <c r="C42" s="26">
         <v>60</v>
       </c>
@@ -21253,7 +21262,7 @@
       <c r="A43" s="14">
         <v>19</v>
       </c>
-      <c r="B43" s="58"/>
+      <c r="B43" s="57"/>
       <c r="C43" s="26">
         <v>80</v>
       </c>
@@ -21496,7 +21505,7 @@
       <c r="A44" s="14">
         <v>19</v>
       </c>
-      <c r="B44" s="59"/>
+      <c r="B44" s="58"/>
       <c r="C44" s="26">
         <v>100</v>
       </c>
@@ -21739,7 +21748,7 @@
       <c r="A45" s="14">
         <v>20</v>
       </c>
-      <c r="B45" s="57" t="s">
+      <c r="B45" s="56" t="s">
         <v>268</v>
       </c>
       <c r="C45" s="26">
@@ -21984,7 +21993,7 @@
       <c r="A46" s="14">
         <v>20</v>
       </c>
-      <c r="B46" s="58"/>
+      <c r="B46" s="57"/>
       <c r="C46" s="26">
         <v>10</v>
       </c>
@@ -22227,7 +22236,7 @@
       <c r="A47" s="14">
         <v>20</v>
       </c>
-      <c r="B47" s="59"/>
+      <c r="B47" s="58"/>
       <c r="C47" s="26">
         <v>20</v>
       </c>
@@ -22470,7 +22479,7 @@
       <c r="A48" s="14">
         <v>21</v>
       </c>
-      <c r="B48" s="57" t="s">
+      <c r="B48" s="56" t="s">
         <v>64</v>
       </c>
       <c r="C48" s="26">
@@ -22715,7 +22724,7 @@
       <c r="A49" s="14">
         <v>21</v>
       </c>
-      <c r="B49" s="58"/>
+      <c r="B49" s="57"/>
       <c r="C49" s="26">
         <v>5</v>
       </c>
@@ -22958,7 +22967,7 @@
       <c r="A50" s="14">
         <v>21</v>
       </c>
-      <c r="B50" s="58"/>
+      <c r="B50" s="57"/>
       <c r="C50" s="26">
         <v>10</v>
       </c>
@@ -23201,7 +23210,7 @@
       <c r="A51" s="14">
         <v>21</v>
       </c>
-      <c r="B51" s="58"/>
+      <c r="B51" s="57"/>
       <c r="C51" s="26">
         <v>15</v>
       </c>
@@ -23444,7 +23453,7 @@
       <c r="A52" s="14">
         <v>21</v>
       </c>
-      <c r="B52" s="59"/>
+      <c r="B52" s="58"/>
       <c r="C52" s="26">
         <v>20</v>
       </c>
@@ -23687,7 +23696,7 @@
       <c r="A53" s="14">
         <v>22</v>
       </c>
-      <c r="B53" s="57" t="s">
+      <c r="B53" s="56" t="s">
         <v>211</v>
       </c>
       <c r="C53" s="26">
@@ -23932,7 +23941,7 @@
       <c r="A54" s="14">
         <v>22</v>
       </c>
-      <c r="B54" s="58"/>
+      <c r="B54" s="57"/>
       <c r="C54" s="26">
         <v>2</v>
       </c>
@@ -24175,7 +24184,7 @@
       <c r="A55" s="14">
         <v>22</v>
       </c>
-      <c r="B55" s="58"/>
+      <c r="B55" s="57"/>
       <c r="C55" s="26">
         <v>4</v>
       </c>
@@ -24418,7 +24427,7 @@
       <c r="A56" s="14">
         <v>22</v>
       </c>
-      <c r="B56" s="58"/>
+      <c r="B56" s="57"/>
       <c r="C56" s="26">
         <v>5</v>
       </c>
@@ -24661,7 +24670,7 @@
       <c r="A57" s="14">
         <v>22</v>
       </c>
-      <c r="B57" s="58"/>
+      <c r="B57" s="57"/>
       <c r="C57" s="26">
         <v>8</v>
       </c>
@@ -24904,7 +24913,7 @@
       <c r="A58" s="14">
         <v>22</v>
       </c>
-      <c r="B58" s="58"/>
+      <c r="B58" s="57"/>
       <c r="C58" s="26">
         <v>15</v>
       </c>
@@ -25147,7 +25156,7 @@
       <c r="A59" s="14">
         <v>22</v>
       </c>
-      <c r="B59" s="59"/>
+      <c r="B59" s="58"/>
       <c r="C59" s="26">
         <v>20</v>
       </c>
@@ -25390,7 +25399,7 @@
       <c r="A60" s="14">
         <v>23</v>
       </c>
-      <c r="B60" s="57" t="s">
+      <c r="B60" s="56" t="s">
         <v>180</v>
       </c>
       <c r="C60" s="26">
@@ -25635,7 +25644,7 @@
       <c r="A61" s="14">
         <v>23</v>
       </c>
-      <c r="B61" s="58"/>
+      <c r="B61" s="57"/>
       <c r="C61" s="26">
         <v>5</v>
       </c>
@@ -25878,7 +25887,7 @@
       <c r="A62" s="14">
         <v>23</v>
       </c>
-      <c r="B62" s="58"/>
+      <c r="B62" s="57"/>
       <c r="C62" s="26">
         <v>10</v>
       </c>
@@ -26121,7 +26130,7 @@
       <c r="A63" s="14">
         <v>23</v>
       </c>
-      <c r="B63" s="58"/>
+      <c r="B63" s="57"/>
       <c r="C63" s="26">
         <v>15</v>
       </c>
@@ -26364,7 +26373,7 @@
       <c r="A64" s="14">
         <v>23</v>
       </c>
-      <c r="B64" s="59"/>
+      <c r="B64" s="58"/>
       <c r="C64" s="26">
         <v>20</v>
       </c>
@@ -26607,7 +26616,7 @@
       <c r="A65" s="14">
         <v>24</v>
       </c>
-      <c r="B65" s="57" t="s">
+      <c r="B65" s="56" t="s">
         <v>210</v>
       </c>
       <c r="C65" s="26">
@@ -26852,7 +26861,7 @@
       <c r="A66" s="14">
         <v>24</v>
       </c>
-      <c r="B66" s="58"/>
+      <c r="B66" s="57"/>
       <c r="C66" s="26">
         <v>5</v>
       </c>
@@ -27095,7 +27104,7 @@
       <c r="A67" s="14">
         <v>24</v>
       </c>
-      <c r="B67" s="58"/>
+      <c r="B67" s="57"/>
       <c r="C67" s="26">
         <v>15</v>
       </c>
@@ -27338,7 +27347,7 @@
       <c r="A68" s="14">
         <v>24</v>
       </c>
-      <c r="B68" s="59"/>
+      <c r="B68" s="58"/>
       <c r="C68" s="26">
         <v>20</v>
       </c>
@@ -27581,7 +27590,7 @@
       <c r="A69" s="14">
         <v>25</v>
       </c>
-      <c r="B69" s="57" t="s">
+      <c r="B69" s="56" t="s">
         <v>216</v>
       </c>
       <c r="C69" s="26">
@@ -27826,7 +27835,7 @@
       <c r="A70" s="14">
         <v>25</v>
       </c>
-      <c r="B70" s="58"/>
+      <c r="B70" s="57"/>
       <c r="C70" s="26">
         <v>3</v>
       </c>
@@ -28069,7 +28078,7 @@
       <c r="A71" s="14">
         <v>25</v>
       </c>
-      <c r="B71" s="58"/>
+      <c r="B71" s="57"/>
       <c r="C71" s="26">
         <v>4</v>
       </c>
@@ -28312,7 +28321,7 @@
       <c r="A72" s="14">
         <v>25</v>
       </c>
-      <c r="B72" s="58"/>
+      <c r="B72" s="57"/>
       <c r="C72" s="26">
         <v>5</v>
       </c>
@@ -28555,7 +28564,7 @@
       <c r="A73" s="14">
         <v>25</v>
       </c>
-      <c r="B73" s="58"/>
+      <c r="B73" s="57"/>
       <c r="C73" s="26">
         <v>6</v>
       </c>
@@ -28798,7 +28807,7 @@
       <c r="A74" s="14">
         <v>25</v>
       </c>
-      <c r="B74" s="58"/>
+      <c r="B74" s="57"/>
       <c r="C74" s="26">
         <v>7</v>
       </c>
@@ -29041,7 +29050,7 @@
       <c r="A75" s="14">
         <v>25</v>
       </c>
-      <c r="B75" s="58"/>
+      <c r="B75" s="57"/>
       <c r="C75" s="26">
         <v>9</v>
       </c>
@@ -29284,7 +29293,7 @@
       <c r="A76" s="14">
         <v>25</v>
       </c>
-      <c r="B76" s="58"/>
+      <c r="B76" s="57"/>
       <c r="C76" s="26">
         <v>11</v>
       </c>
@@ -29527,7 +29536,7 @@
       <c r="A77" s="14">
         <v>25</v>
       </c>
-      <c r="B77" s="58"/>
+      <c r="B77" s="57"/>
       <c r="C77" s="26">
         <v>13</v>
       </c>
@@ -29770,7 +29779,7 @@
       <c r="A78" s="14">
         <v>25</v>
       </c>
-      <c r="B78" s="58"/>
+      <c r="B78" s="57"/>
       <c r="C78" s="26">
         <v>15</v>
       </c>
@@ -30013,7 +30022,7 @@
       <c r="A79" s="14">
         <v>25</v>
       </c>
-      <c r="B79" s="58"/>
+      <c r="B79" s="57"/>
       <c r="C79" s="26">
         <v>17</v>
       </c>
@@ -30256,7 +30265,7 @@
       <c r="A80" s="14">
         <v>25</v>
       </c>
-      <c r="B80" s="58"/>
+      <c r="B80" s="57"/>
       <c r="C80" s="26">
         <v>19</v>
       </c>
@@ -30499,7 +30508,7 @@
       <c r="A81" s="14">
         <v>25</v>
       </c>
-      <c r="B81" s="58"/>
+      <c r="B81" s="57"/>
       <c r="C81" s="26">
         <v>21</v>
       </c>
@@ -30742,7 +30751,7 @@
       <c r="A82" s="14">
         <v>25</v>
       </c>
-      <c r="B82" s="58"/>
+      <c r="B82" s="57"/>
       <c r="C82" s="26">
         <v>23</v>
       </c>
@@ -30985,7 +30994,7 @@
       <c r="A83" s="14">
         <v>25</v>
       </c>
-      <c r="B83" s="58"/>
+      <c r="B83" s="57"/>
       <c r="C83" s="26">
         <v>25</v>
       </c>
@@ -31228,7 +31237,7 @@
       <c r="A84" s="14">
         <v>25</v>
       </c>
-      <c r="B84" s="58"/>
+      <c r="B84" s="57"/>
       <c r="C84" s="26">
         <v>27</v>
       </c>
@@ -31471,7 +31480,7 @@
       <c r="A85" s="14">
         <v>25</v>
       </c>
-      <c r="B85" s="58"/>
+      <c r="B85" s="57"/>
       <c r="C85" s="26">
         <v>29</v>
       </c>
@@ -31714,7 +31723,7 @@
       <c r="A86" s="14">
         <v>25</v>
       </c>
-      <c r="B86" s="58"/>
+      <c r="B86" s="57"/>
       <c r="C86" s="26">
         <v>31</v>
       </c>
@@ -31957,7 +31966,7 @@
       <c r="A87" s="14">
         <v>25</v>
       </c>
-      <c r="B87" s="59"/>
+      <c r="B87" s="58"/>
       <c r="C87" s="26">
         <v>33</v>
       </c>
@@ -32203,7 +32212,7 @@
       <c r="B88" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="54"/>
+      <c r="C88" s="53"/>
       <c r="D88" s="26" t="s">
         <v>80</v>
       </c>
@@ -32446,7 +32455,7 @@
       <c r="B89" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C89" s="56"/>
+      <c r="C89" s="55"/>
       <c r="D89" s="26" t="s">
         <v>81</v>
       </c>
@@ -35855,10 +35864,10 @@
       <c r="A103" s="14">
         <v>38</v>
       </c>
-      <c r="B103" s="62" t="s">
+      <c r="B103" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="C103" s="63"/>
+      <c r="C103" s="62"/>
       <c r="D103" s="26" t="s">
         <v>53</v>
       </c>
@@ -36098,10 +36107,10 @@
       <c r="A104" s="14">
         <v>39</v>
       </c>
-      <c r="B104" s="60" t="s">
+      <c r="B104" s="59" t="s">
         <v>207</v>
       </c>
-      <c r="C104" s="61"/>
+      <c r="C104" s="60"/>
       <c r="D104" s="26" t="s">
         <v>53</v>
       </c>
@@ -38289,10 +38298,10 @@
       <c r="A113" s="14">
         <v>47</v>
       </c>
-      <c r="B113" s="57" t="s">
+      <c r="B113" s="56" t="s">
         <v>110</v>
       </c>
-      <c r="C113" s="54"/>
+      <c r="C113" s="53"/>
       <c r="D113" s="26" t="s">
         <v>123</v>
       </c>
@@ -38532,8 +38541,8 @@
       <c r="A114" s="14">
         <v>48</v>
       </c>
-      <c r="B114" s="59"/>
-      <c r="C114" s="56"/>
+      <c r="B114" s="58"/>
+      <c r="C114" s="55"/>
       <c r="D114" s="26" t="s">
         <v>124</v>
       </c>
@@ -38773,10 +38782,10 @@
       <c r="A115" s="14">
         <v>49</v>
       </c>
-      <c r="B115" s="57" t="s">
+      <c r="B115" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="C115" s="54"/>
+      <c r="C115" s="53"/>
       <c r="D115" s="26" t="s">
         <v>58</v>
       </c>
@@ -39016,8 +39025,8 @@
       <c r="A116" s="14">
         <v>50</v>
       </c>
-      <c r="B116" s="59"/>
-      <c r="C116" s="56"/>
+      <c r="B116" s="58"/>
+      <c r="C116" s="55"/>
       <c r="D116" s="26" t="s">
         <v>125</v>
       </c>
@@ -39257,10 +39266,10 @@
       <c r="A117" s="14">
         <v>51</v>
       </c>
-      <c r="B117" s="57" t="s">
+      <c r="B117" s="56" t="s">
         <v>266</v>
       </c>
-      <c r="C117" s="54"/>
+      <c r="C117" s="53"/>
       <c r="D117" s="26" t="s">
         <v>58</v>
       </c>
@@ -39500,8 +39509,8 @@
       <c r="A118" s="14">
         <v>52</v>
       </c>
-      <c r="B118" s="59"/>
-      <c r="C118" s="56"/>
+      <c r="B118" s="58"/>
+      <c r="C118" s="55"/>
       <c r="D118" s="26" t="s">
         <v>125</v>
       </c>
@@ -39741,10 +39750,10 @@
       <c r="A119" s="14">
         <v>53</v>
       </c>
-      <c r="B119" s="57" t="s">
+      <c r="B119" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="C119" s="54"/>
+      <c r="C119" s="53"/>
       <c r="D119" s="26" t="s">
         <v>80</v>
       </c>
@@ -39984,8 +39993,8 @@
       <c r="A120" s="14">
         <v>54</v>
       </c>
-      <c r="B120" s="59"/>
-      <c r="C120" s="56"/>
+      <c r="B120" s="58"/>
+      <c r="C120" s="55"/>
       <c r="D120" s="26" t="s">
         <v>115</v>
       </c>
@@ -40225,10 +40234,10 @@
       <c r="A121" s="14">
         <v>55</v>
       </c>
-      <c r="B121" s="57" t="s">
+      <c r="B121" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="C121" s="54"/>
+      <c r="C121" s="53"/>
       <c r="D121" s="26" t="s">
         <v>80</v>
       </c>
@@ -40468,8 +40477,8 @@
       <c r="A122" s="14">
         <v>56</v>
       </c>
-      <c r="B122" s="59"/>
-      <c r="C122" s="56"/>
+      <c r="B122" s="58"/>
+      <c r="C122" s="55"/>
       <c r="D122" s="26" t="s">
         <v>99</v>
       </c>
@@ -40712,7 +40721,7 @@
       <c r="B123" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="C123" s="54"/>
+      <c r="C123" s="53"/>
       <c r="D123" s="26" t="s">
         <v>80</v>
       </c>
@@ -40955,7 +40964,7 @@
       <c r="B124" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="C124" s="56"/>
+      <c r="C124" s="55"/>
       <c r="D124" s="26" t="s">
         <v>115</v>
       </c>
@@ -41195,10 +41204,10 @@
       <c r="A125" s="14">
         <v>59</v>
       </c>
-      <c r="B125" s="66" t="s">
+      <c r="B125" s="65" t="s">
         <v>265</v>
       </c>
-      <c r="C125" s="67"/>
+      <c r="C125" s="66"/>
       <c r="D125" s="26" t="s">
         <v>160</v>
       </c>
@@ -41438,10 +41447,10 @@
       <c r="A126" s="14">
         <v>60</v>
       </c>
-      <c r="B126" s="64" t="s">
+      <c r="B126" s="63" t="s">
         <v>161</v>
       </c>
-      <c r="C126" s="65"/>
+      <c r="C126" s="64"/>
       <c r="D126" s="26" t="s">
         <v>158</v>
       </c>
@@ -41681,10 +41690,10 @@
       <c r="A127" s="14">
         <v>61</v>
       </c>
-      <c r="B127" s="57" t="s">
+      <c r="B127" s="56" t="s">
         <v>227</v>
       </c>
-      <c r="C127" s="54"/>
+      <c r="C127" s="53"/>
       <c r="D127" s="26" t="s">
         <v>159</v>
       </c>
@@ -41924,8 +41933,8 @@
       <c r="A128" s="14">
         <v>62</v>
       </c>
-      <c r="B128" s="59"/>
-      <c r="C128" s="56"/>
+      <c r="B128" s="58"/>
+      <c r="C128" s="55"/>
       <c r="D128" s="26" t="s">
         <v>158</v>
       </c>
@@ -44109,10 +44118,10 @@
       <c r="A137" s="14">
         <v>71</v>
       </c>
-      <c r="B137" s="68" t="s">
+      <c r="B137" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="C137" s="54"/>
+      <c r="C137" s="53"/>
       <c r="D137" s="26" t="s">
         <v>155</v>
       </c>
@@ -44352,8 +44361,8 @@
       <c r="A138" s="14">
         <v>72</v>
       </c>
-      <c r="B138" s="69"/>
-      <c r="C138" s="56"/>
+      <c r="B138" s="68"/>
+      <c r="C138" s="55"/>
       <c r="D138" s="26" t="s">
         <v>154</v>
       </c>
@@ -45079,10 +45088,10 @@
       <c r="A141" s="14">
         <v>75</v>
       </c>
-      <c r="B141" s="57" t="s">
+      <c r="B141" s="56" t="s">
         <v>262</v>
       </c>
-      <c r="C141" s="54"/>
+      <c r="C141" s="53"/>
       <c r="D141" s="26" t="s">
         <v>152</v>
       </c>
@@ -45322,8 +45331,8 @@
       <c r="A142" s="14">
         <v>76</v>
       </c>
-      <c r="B142" s="58"/>
-      <c r="C142" s="55"/>
+      <c r="B142" s="57"/>
+      <c r="C142" s="54"/>
       <c r="D142" s="26" t="s">
         <v>151</v>
       </c>
@@ -45563,8 +45572,8 @@
       <c r="A143" s="14">
         <v>77</v>
       </c>
-      <c r="B143" s="58"/>
-      <c r="C143" s="55"/>
+      <c r="B143" s="57"/>
+      <c r="C143" s="54"/>
       <c r="D143" s="26" t="s">
         <v>150</v>
       </c>
@@ -45804,8 +45813,8 @@
       <c r="A144" s="14">
         <v>78</v>
       </c>
-      <c r="B144" s="59"/>
-      <c r="C144" s="56"/>
+      <c r="B144" s="58"/>
+      <c r="C144" s="55"/>
       <c r="D144" s="26" t="s">
         <v>149</v>
       </c>
@@ -46045,10 +46054,10 @@
       <c r="A145" s="14">
         <v>79</v>
       </c>
-      <c r="B145" s="57" t="s">
+      <c r="B145" s="56" t="s">
         <v>261</v>
       </c>
-      <c r="C145" s="54"/>
+      <c r="C145" s="53"/>
       <c r="D145" s="26" t="s">
         <v>57</v>
       </c>
@@ -46288,8 +46297,8 @@
       <c r="A146" s="14">
         <v>80</v>
       </c>
-      <c r="B146" s="58"/>
-      <c r="C146" s="55"/>
+      <c r="B146" s="57"/>
+      <c r="C146" s="54"/>
       <c r="D146" s="26" t="s">
         <v>148</v>
       </c>
@@ -46529,8 +46538,8 @@
       <c r="A147" s="14">
         <v>81</v>
       </c>
-      <c r="B147" s="58"/>
-      <c r="C147" s="55"/>
+      <c r="B147" s="57"/>
+      <c r="C147" s="54"/>
       <c r="D147" s="26" t="s">
         <v>147</v>
       </c>
@@ -46770,8 +46779,8 @@
       <c r="A148" s="14">
         <v>82</v>
       </c>
-      <c r="B148" s="59"/>
-      <c r="C148" s="56"/>
+      <c r="B148" s="58"/>
+      <c r="C148" s="55"/>
       <c r="D148" s="26" t="s">
         <v>146</v>
       </c>
@@ -47254,10 +47263,10 @@
       <c r="A150" s="14">
         <v>84</v>
       </c>
-      <c r="B150" s="57" t="s">
+      <c r="B150" s="56" t="s">
         <v>259</v>
       </c>
-      <c r="C150" s="54"/>
+      <c r="C150" s="53"/>
       <c r="D150" s="26" t="s">
         <v>144</v>
       </c>
@@ -47497,8 +47506,8 @@
       <c r="A151" s="14">
         <v>85</v>
       </c>
-      <c r="B151" s="59"/>
-      <c r="C151" s="56"/>
+      <c r="B151" s="58"/>
+      <c r="C151" s="55"/>
       <c r="D151" s="26" t="s">
         <v>58</v>
       </c>
@@ -47738,10 +47747,10 @@
       <c r="A152" s="14">
         <v>86</v>
       </c>
-      <c r="B152" s="57" t="s">
+      <c r="B152" s="56" t="s">
         <v>258</v>
       </c>
-      <c r="C152" s="54"/>
+      <c r="C152" s="53"/>
       <c r="D152" s="26" t="s">
         <v>57</v>
       </c>
@@ -47981,8 +47990,8 @@
       <c r="A153" s="14">
         <v>87</v>
       </c>
-      <c r="B153" s="58"/>
-      <c r="C153" s="55"/>
+      <c r="B153" s="57"/>
+      <c r="C153" s="54"/>
       <c r="D153" s="26" t="s">
         <v>143</v>
       </c>
@@ -48222,8 +48231,8 @@
       <c r="A154" s="14">
         <v>88</v>
       </c>
-      <c r="B154" s="59"/>
-      <c r="C154" s="56"/>
+      <c r="B154" s="58"/>
+      <c r="C154" s="55"/>
       <c r="D154" s="26" t="s">
         <v>140</v>
       </c>
@@ -48463,10 +48472,10 @@
       <c r="A155" s="14">
         <v>89</v>
       </c>
-      <c r="B155" s="57" t="s">
+      <c r="B155" s="56" t="s">
         <v>234</v>
       </c>
-      <c r="C155" s="54"/>
+      <c r="C155" s="53"/>
       <c r="D155" s="26" t="s">
         <v>57</v>
       </c>
@@ -48706,8 +48715,8 @@
       <c r="A156" s="14">
         <v>90</v>
       </c>
-      <c r="B156" s="59"/>
-      <c r="C156" s="56"/>
+      <c r="B156" s="58"/>
+      <c r="C156" s="55"/>
       <c r="D156" s="26" t="s">
         <v>142</v>
       </c>
@@ -49433,10 +49442,10 @@
       <c r="A159" s="14">
         <v>93</v>
       </c>
-      <c r="B159" s="57" t="s">
+      <c r="B159" s="56" t="s">
         <v>257</v>
       </c>
-      <c r="C159" s="54"/>
+      <c r="C159" s="53"/>
       <c r="D159" s="26" t="s">
         <v>141</v>
       </c>
@@ -49676,8 +49685,8 @@
       <c r="A160" s="14">
         <v>94</v>
       </c>
-      <c r="B160" s="59"/>
-      <c r="C160" s="56"/>
+      <c r="B160" s="58"/>
+      <c r="C160" s="55"/>
       <c r="D160" s="26" t="s">
         <v>140</v>
       </c>
@@ -49917,10 +49926,10 @@
       <c r="A161" s="14">
         <v>95</v>
       </c>
-      <c r="B161" s="57" t="s">
+      <c r="B161" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="C161" s="54"/>
+      <c r="C161" s="53"/>
       <c r="D161" s="26" t="s">
         <v>60</v>
       </c>
@@ -50160,8 +50169,8 @@
       <c r="A162" s="14">
         <v>96</v>
       </c>
-      <c r="B162" s="58"/>
-      <c r="C162" s="55"/>
+      <c r="B162" s="57"/>
+      <c r="C162" s="54"/>
       <c r="D162" s="26" t="s">
         <v>139</v>
       </c>
@@ -50401,8 +50410,8 @@
       <c r="A163" s="14">
         <v>97</v>
       </c>
-      <c r="B163" s="58"/>
-      <c r="C163" s="55"/>
+      <c r="B163" s="57"/>
+      <c r="C163" s="54"/>
       <c r="D163" s="26" t="s">
         <v>138</v>
       </c>
@@ -50642,8 +50651,8 @@
       <c r="A164" s="14">
         <v>98</v>
       </c>
-      <c r="B164" s="59"/>
-      <c r="C164" s="56"/>
+      <c r="B164" s="58"/>
+      <c r="C164" s="55"/>
       <c r="D164" s="26" t="s">
         <v>137</v>
       </c>
@@ -51369,7 +51378,7 @@
       <c r="A167" s="14">
         <v>101</v>
       </c>
-      <c r="B167" s="57" t="s">
+      <c r="B167" s="56" t="s">
         <v>203</v>
       </c>
       <c r="C167" s="26">
@@ -51614,7 +51623,7 @@
       <c r="A168" s="14">
         <v>101</v>
       </c>
-      <c r="B168" s="58"/>
+      <c r="B168" s="57"/>
       <c r="C168" s="26">
         <v>10</v>
       </c>
@@ -51857,7 +51866,7 @@
       <c r="A169" s="14">
         <v>101</v>
       </c>
-      <c r="B169" s="59"/>
+      <c r="B169" s="58"/>
       <c r="C169" s="26">
         <v>20</v>
       </c>
@@ -60851,7 +60860,7 @@
       <c r="B206" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="C206" s="54"/>
+      <c r="C206" s="53"/>
       <c r="D206" s="26" t="s">
         <v>100</v>
       </c>
@@ -61094,7 +61103,7 @@
       <c r="B207" s="34" t="s">
         <v>255</v>
       </c>
-      <c r="C207" s="56"/>
+      <c r="C207" s="55"/>
       <c r="D207" s="26" t="s">
         <v>101</v>
       </c>
@@ -64979,10 +64988,10 @@
       <c r="A223" s="14">
         <v>155</v>
       </c>
-      <c r="B223" s="57" t="s">
+      <c r="B223" s="56" t="s">
         <v>187</v>
       </c>
-      <c r="C223" s="54"/>
+      <c r="C223" s="53"/>
       <c r="D223" s="26" t="s">
         <v>52</v>
       </c>
@@ -65222,8 +65231,8 @@
       <c r="A224" s="14">
         <v>156</v>
       </c>
-      <c r="B224" s="58"/>
-      <c r="C224" s="55"/>
+      <c r="B224" s="57"/>
+      <c r="C224" s="54"/>
       <c r="D224" s="26" t="s">
         <v>50</v>
       </c>
@@ -65463,8 +65472,8 @@
       <c r="A225" s="14">
         <v>157</v>
       </c>
-      <c r="B225" s="59"/>
-      <c r="C225" s="56"/>
+      <c r="B225" s="58"/>
+      <c r="C225" s="55"/>
       <c r="D225" s="26" t="s">
         <v>51</v>
       </c>
@@ -67345,6 +67354,13 @@
     <mergeCell ref="B145:B148"/>
     <mergeCell ref="C145:C148"/>
     <mergeCell ref="B137:B138"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="B159:B160"/>
+    <mergeCell ref="C159:C160"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="C115:C116"/>
+    <mergeCell ref="C150:C151"/>
     <mergeCell ref="B152:B154"/>
     <mergeCell ref="B155:B156"/>
     <mergeCell ref="C137:C138"/>
@@ -67355,13 +67371,6 @@
     <mergeCell ref="B126:C126"/>
     <mergeCell ref="B125:C125"/>
     <mergeCell ref="B127:B128"/>
-    <mergeCell ref="B159:B160"/>
-    <mergeCell ref="C159:C160"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="C115:C116"/>
-    <mergeCell ref="C113:C114"/>
-    <mergeCell ref="C150:C151"/>
     <mergeCell ref="B29:B32"/>
     <mergeCell ref="B113:B114"/>
     <mergeCell ref="B115:B116"/>
@@ -67384,9 +67393,6 @@
     <mergeCell ref="B19:B23"/>
     <mergeCell ref="B24:B28"/>
   </mergeCells>
-  <conditionalFormatting sqref="F3:Y3">
-    <cfRule type="top10" dxfId="2" priority="1" rank="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F3:Y225">
     <cfRule type="colorScale" priority="5">
       <colorScale>
@@ -67410,12 +67416,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3:AS225">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV3:BO225">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -67448,7 +67454,7 @@
       <c r="B2" s="1">
         <v>0.98799699924981255</v>
       </c>
-      <c r="E2" s="50"/>
+      <c r="E2" s="49"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -67457,7 +67463,7 @@
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" s="50"/>
+      <c r="E3" s="49"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -67466,7 +67472,7 @@
       <c r="B4" s="1">
         <v>1.187921980495124</v>
       </c>
-      <c r="E4" s="50"/>
+      <c r="E4" s="49"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -67475,7 +67481,7 @@
       <c r="B5" s="1">
         <v>1.2104276069017255</v>
       </c>
-      <c r="E5" s="50"/>
+      <c r="E5" s="49"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -67484,7 +67490,7 @@
       <c r="B6" s="1">
         <v>1.2111777944486122</v>
       </c>
-      <c r="E6" s="50"/>
+      <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -67493,7 +67499,7 @@
       <c r="B7" s="1">
         <v>1.3060765191297825</v>
       </c>
-      <c r="E7" s="50"/>
+      <c r="E7" s="49"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -67502,7 +67508,7 @@
       <c r="B8" s="1">
         <v>1.3087021755438861</v>
       </c>
-      <c r="E8" s="50"/>
+      <c r="E8" s="49"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -67511,7 +67517,7 @@
       <c r="B9" s="1">
         <v>1.3132033008252064</v>
       </c>
-      <c r="E9" s="50"/>
+      <c r="E9" s="49"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -67520,7 +67526,7 @@
       <c r="B10" s="1">
         <v>1.4579894973743437</v>
       </c>
-      <c r="E10" s="50"/>
+      <c r="E10" s="49"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -67529,7 +67535,7 @@
       <c r="B11" s="1">
         <v>1.4722430607651915</v>
       </c>
-      <c r="E11" s="50"/>
+      <c r="E11" s="49"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -67538,7 +67544,7 @@
       <c r="B12" s="1">
         <v>1.6395348837209305</v>
       </c>
-      <c r="E12" s="50"/>
+      <c r="E12" s="49"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -67547,7 +67553,7 @@
       <c r="B13" s="1">
         <v>1.9054763690922731</v>
       </c>
-      <c r="E13" s="50"/>
+      <c r="E13" s="49"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -67556,7 +67562,7 @@
       <c r="B14" s="1">
         <v>1.9951237809452365</v>
       </c>
-      <c r="E14" s="50"/>
+      <c r="E14" s="49"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -67565,7 +67571,7 @@
       <c r="B15" s="1">
         <v>2.2490622655663914</v>
       </c>
-      <c r="E15" s="50"/>
+      <c r="E15" s="49"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -67574,7 +67580,7 @@
       <c r="B16" s="1">
         <v>2.3713428357089272</v>
       </c>
-      <c r="E16" s="50"/>
+      <c r="E16" s="49"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
@@ -67583,7 +67589,7 @@
       <c r="B17" s="1">
         <v>3.2269317329332332</v>
       </c>
-      <c r="E17" s="50"/>
+      <c r="E17" s="49"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
@@ -67592,7 +67598,7 @@
       <c r="B18" s="1">
         <v>3.7996999249812453</v>
       </c>
-      <c r="E18" s="50"/>
+      <c r="E18" s="49"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
@@ -67601,7 +67607,7 @@
       <c r="B19" s="1">
         <v>5.2393098274568644</v>
       </c>
-      <c r="E19" s="50"/>
+      <c r="E19" s="49"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
@@ -67610,7 +67616,7 @@
       <c r="B20" s="1">
         <v>9.1069017254313582</v>
       </c>
-      <c r="E20" s="50"/>
+      <c r="E20" s="49"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
@@ -67619,7 +67625,7 @@
       <c r="B21" s="1">
         <v>33.460990247561895</v>
       </c>
-      <c r="E21" s="50"/>
+      <c r="E21" s="49"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D2:E21">
